--- a/Top50.xlsx
+++ b/Top50.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="489">
   <si>
     <t>GROUPE HOTE</t>
   </si>
@@ -1504,6 +1504,9 @@
   </si>
   <si>
     <t>ND</t>
+  </si>
+  <si>
+    <t>SYTHD00000</t>
   </si>
 </sst>
 </file>
@@ -1830,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -4923,6 +4926,11 @@
       </c>
       <c r="F178" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B179" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
